--- a/education_forms/036_global_education_conference_registration_form--education_forms.xlsx
+++ b/education_forms/036_global_education_conference_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>date_of_birth_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Date Of Birth 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>time_of_submission</t>
+          <t>time_of_submission_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Time of Submission</t>
+          <t>Time Of Submission 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How would you describe the purpose of your registration?</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submit_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,148 +1216,114 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
